--- a/EntreesCDA/ig/StructureDefinition-fr-cda-instructions-au-dispensateur.xlsx
+++ b/EntreesCDA/ig/StructureDefinition-fr-cda-instructions-au-dispensateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T13:12:24+00:00</t>
+    <t>2026-04-20T13:35:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5184,7 +5184,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>192</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
